--- a/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
+++ b/2_datos/1_raw/7_columnas_dataset_rezago_epi.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\3_xgboost\2_datos\1_raw\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\marco\Documentos\investigacion\machine_learning_idalina\4_LightGBM\2_datos\1_raw\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44E80719-6639-4D80-A404-726A2799EA51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4BE7F908-7BD2-486F-8852-FEFF213C6C00}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -74,8 +74,16 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -103,8 +111,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -427,70 +436,71 @@
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>4</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>6</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A9" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
     </row>
     <row r="10" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A10" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A11" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
     </row>
     <row r="13" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
     </row>
     <row r="14" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A14" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:1" x14ac:dyDescent="0.35">
       <c r="A15" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
     </row>
     <row r="16" spans="1:1" x14ac:dyDescent="0.35">
-      <c r="A16" t="s">
-        <v>15</v>
+      <c r="A16" s="1" t="s">
+        <v>3</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>